--- a/gk-league-comparison/data/FIN1_2026.xlsx
+++ b/gk-league-comparison/data/FIN1_2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr date1904="false"/>
   <sheets>
-    <sheet name="Search results (14)" sheetId="1" r:id="rId4"/>
+    <sheet name="Search results (16)" sheetId="1" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -67,7 +67,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:DY15"/>
+  <dimension ref="A1:DY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="12.989887640449439"/>
@@ -80,7 +80,7 @@
     <col min="8" max="8" bestFit="true" customWidth="true" width="11.88988764044944"/>
     <col min="9" max="9" bestFit="true" customWidth="true" width="12.989887640449439"/>
     <col min="10" max="10" bestFit="true" customWidth="true" width="5.289887640449439"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="5.289887640449439"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="6.389887640449439"/>
     <col min="12" max="12" bestFit="true" customWidth="true" width="4.189887640449439"/>
     <col min="13" max="13" bestFit="true" customWidth="true" width="6.389887640449439"/>
     <col min="14" max="14" bestFit="true" customWidth="true" width="12.989887640449439"/>
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="H2" s="0" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>1448</v>
+        <v>2014</v>
       </c>
       <c r="J2" s="0" t="n">
         <v>0</v>
@@ -899,7 +899,7 @@
         <v>0.0</v>
       </c>
       <c r="N2" s="0" t="n">
-        <v>0.81</v>
+        <v>0.71</v>
       </c>
       <c r="O2" s="0" t="n">
         <v>100.0</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="V2" s="0" t="n">
-        <v>1.31</v>
+        <v>0.98</v>
       </c>
       <c r="W2" s="0" t="n">
         <v>0.0</v>
@@ -940,7 +940,7 @@
         <v>0.0</v>
       </c>
       <c r="Y2" s="0" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="Z2" s="0" t="n">
         <v>100.0</v>
@@ -955,10 +955,10 @@
         <v>0.0</v>
       </c>
       <c r="AD2" s="0" t="n">
-        <v>1.31</v>
+        <v>0.98</v>
       </c>
       <c r="AE2" s="0" t="n">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="AF2" s="0" t="n">
         <v>0.0</v>
@@ -976,7 +976,7 @@
         <v>0.0</v>
       </c>
       <c r="AK2" s="0" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AL2" s="0" t="n">
         <v>0.0</v>
@@ -1033,13 +1033,13 @@
         <v>0.0</v>
       </c>
       <c r="BD2" s="0" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BE2" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="BF2" s="0" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BG2" s="0" t="n">
         <v>100.0</v>
@@ -1051,58 +1051,58 @@
         <v>0.0</v>
       </c>
       <c r="BJ2" s="0" t="n">
-        <v>0.0</v>
+        <v>0.09</v>
       </c>
       <c r="BK2" s="0" t="n">
-        <v>33.69</v>
+        <v>32.76</v>
       </c>
       <c r="BL2" s="0" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BM2" s="0" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="BN2" s="0" t="n">
-        <v>45.44</v>
+        <v>44.46</v>
       </c>
       <c r="BO2" s="0" t="n">
-        <v>84.82</v>
+        <v>83.92</v>
       </c>
       <c r="BP2" s="0" t="n">
-        <v>26.17</v>
+        <v>25.56</v>
       </c>
       <c r="BQ2" s="0" t="n">
-        <v>76.01</v>
+        <v>75.0</v>
       </c>
       <c r="BR2" s="0" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="BS2" s="0" t="n">
-        <v>0.0</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" s="0" t="n">
-        <v>17.9</v>
+        <v>17.65</v>
       </c>
       <c r="BU2" s="0" t="n">
-        <v>97.22</v>
+        <v>96.71</v>
       </c>
       <c r="BV2" s="0" t="n">
-        <v>31.7</v>
+        <v>30.57</v>
       </c>
       <c r="BW2" s="0" t="n">
-        <v>95.29</v>
+        <v>95.61</v>
       </c>
       <c r="BX2" s="0" t="n">
-        <v>13.55</v>
+        <v>13.67</v>
       </c>
       <c r="BY2" s="0" t="n">
-        <v>61.47</v>
+        <v>59.15</v>
       </c>
       <c r="BZ2" s="0" t="n">
-        <v>29.59</v>
+        <v>30.41</v>
       </c>
       <c r="CA2" s="0" t="n">
-        <v>48.12</v>
+        <v>48.42</v>
       </c>
       <c r="CB2" s="0" t="n">
         <v>0.0</v>
@@ -1126,73 +1126,73 @@
         <v>0.0</v>
       </c>
       <c r="CI2" s="0" t="n">
-        <v>5.9</v>
+        <v>6.26</v>
       </c>
       <c r="CJ2" s="0" t="n">
-        <v>54.74</v>
+        <v>51.43</v>
       </c>
       <c r="CK2" s="0" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="CL2" s="0" t="n">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="CM2" s="0" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="CN2" s="0" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="CO2" s="0" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="CP2" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ2" s="0" t="n">
-        <v>11.0</v>
+        <v>10.64</v>
       </c>
       <c r="CR2" s="0" t="n">
-        <v>74.01</v>
+        <v>73.11</v>
       </c>
       <c r="CS2" s="0" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="CT2" s="0" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="CU2" s="0" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="CV2" s="0" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="CW2" s="0" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CX2" s="0" t="n">
-        <v>74.14</v>
+        <v>71.79</v>
       </c>
       <c r="CY2" s="0" t="n">
-        <v>16.87</v>
+        <v>23.72</v>
       </c>
       <c r="CZ2" s="0" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="DA2" s="0" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="DB2" s="0" t="n">
-        <v>0.116</v>
+        <v>0.077</v>
       </c>
       <c r="DC2" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD2" s="0" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="DE2" s="0" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="DF2" s="0" t="inlineStr">
         <is>
@@ -1264,17 +1264,17 @@
     <row ht="12" customHeight="true" r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>M. Marković</t>
+          <t>Otso Virtanen</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="E3" s="0" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>350000</v>
+        <v>250000</v>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="H3" s="0" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>1129</v>
+        <v>794</v>
       </c>
       <c r="J3" s="0" t="n">
         <v>0</v>
@@ -1312,19 +1312,19 @@
         <v>0.0</v>
       </c>
       <c r="N3" s="0" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>76.92</v>
+        <v>88.89</v>
       </c>
       <c r="P3" s="0" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="Q3" s="0" t="inlineStr">
         <is>
-          <t>Croatia, Bosnia and Herzegovina</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="R3" s="0" t="inlineStr">
@@ -1333,54 +1333,54 @@
         </is>
       </c>
       <c r="S3" s="0" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="T3" s="0" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="U3" s="0" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V3" s="0" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="W3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.23</v>
       </c>
       <c r="X3" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="Y3" s="0" t="n">
-        <v>0.72</v>
+        <v>0.34</v>
       </c>
       <c r="Z3" s="0" t="n">
-        <v>77.78</v>
+        <v>100.0</v>
       </c>
       <c r="AA3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.11</v>
       </c>
       <c r="AB3" s="0" t="n">
-        <v>0.0</v>
+        <v>0.12</v>
       </c>
       <c r="AC3" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="AD3" s="0" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="AE3" s="0" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="AF3" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="AG3" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="0" t="n">
-        <v>0.08</v>
+        <v>0.0</v>
       </c>
       <c r="AI3" s="0" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0.0</v>
       </c>
       <c r="BF3" s="0" t="n">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="BG3" s="0" t="n">
         <v>100.0</v>
@@ -1467,25 +1467,25 @@
         <v>0.0</v>
       </c>
       <c r="BK3" s="0" t="n">
-        <v>13.95</v>
+        <v>14.96</v>
       </c>
       <c r="BL3" s="0" t="n">
-        <v>0.48</v>
+        <v>0.11</v>
       </c>
       <c r="BM3" s="0" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="BN3" s="0" t="n">
-        <v>22.8</v>
+        <v>25.16</v>
       </c>
       <c r="BO3" s="0" t="n">
-        <v>90.21</v>
+        <v>79.28</v>
       </c>
       <c r="BP3" s="0" t="n">
-        <v>11.16</v>
+        <v>12.02</v>
       </c>
       <c r="BQ3" s="0" t="n">
-        <v>83.57</v>
+        <v>58.49</v>
       </c>
       <c r="BR3" s="0" t="n">
         <v>0.0</v>
@@ -1494,28 +1494,28 @@
         <v>0.0</v>
       </c>
       <c r="BT3" s="0" t="n">
-        <v>10.36</v>
+        <v>10.99</v>
       </c>
       <c r="BU3" s="0" t="n">
-        <v>96.15</v>
+        <v>97.94</v>
       </c>
       <c r="BV3" s="0" t="n">
-        <v>18.1</v>
+        <v>16.44</v>
       </c>
       <c r="BW3" s="0" t="n">
-        <v>96.48</v>
+        <v>97.93</v>
       </c>
       <c r="BX3" s="0" t="n">
-        <v>4.7</v>
+        <v>8.73</v>
       </c>
       <c r="BY3" s="0" t="n">
-        <v>66.1</v>
+        <v>44.16</v>
       </c>
       <c r="BZ3" s="0" t="n">
-        <v>24.25</v>
+        <v>30.54</v>
       </c>
       <c r="CA3" s="0" t="n">
-        <v>44.75</v>
+        <v>51.76</v>
       </c>
       <c r="CB3" s="0" t="n">
         <v>0.0</v>
@@ -1539,19 +1539,19 @@
         <v>0.0</v>
       </c>
       <c r="CI3" s="0" t="n">
-        <v>0.72</v>
+        <v>3.74</v>
       </c>
       <c r="CJ3" s="0" t="n">
-        <v>44.44</v>
+        <v>39.39</v>
       </c>
       <c r="CK3" s="0" t="n">
-        <v>0.08</v>
+        <v>0.57</v>
       </c>
       <c r="CL3" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CM3" s="0" t="n">
-        <v>0.08</v>
+        <v>0.0</v>
       </c>
       <c r="CN3" s="0" t="n">
         <v>0.0</v>
@@ -1563,49 +1563,49 @@
         <v>0.0</v>
       </c>
       <c r="CQ3" s="0" t="n">
-        <v>3.91</v>
+        <v>5.44</v>
       </c>
       <c r="CR3" s="0" t="n">
-        <v>61.22</v>
+        <v>60.42</v>
       </c>
       <c r="CS3" s="0" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CT3" s="0" t="n">
-        <v>0.88</v>
+        <v>1.7</v>
       </c>
       <c r="CU3" s="0" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="CV3" s="0" t="n">
-        <v>3.67</v>
+        <v>4.99</v>
       </c>
       <c r="CW3" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CX3" s="0" t="n">
-        <v>76.09</v>
+        <v>65.91</v>
       </c>
       <c r="CY3" s="0" t="n">
-        <v>12.3</v>
+        <v>14.57</v>
       </c>
       <c r="CZ3" s="0" t="n">
-        <v>0.98</v>
+        <v>1.65</v>
       </c>
       <c r="DA3" s="0" t="n">
-        <v>1.3</v>
+        <v>-0.43</v>
       </c>
       <c r="DB3" s="0" t="n">
-        <v>0.104</v>
+        <v>-0.049</v>
       </c>
       <c r="DC3" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD3" s="0" t="n">
-        <v>2.23</v>
+        <v>2.72</v>
       </c>
       <c r="DE3" s="0" t="n">
-        <v>0.72</v>
+        <v>0.34</v>
       </c>
       <c r="DF3" s="0" t="inlineStr">
         <is>
@@ -1632,62 +1632,62 @@
         <v>0.0</v>
       </c>
       <c r="DL3" s="0" t="n">
-        <v>5491.34</v>
+        <v>6514.08</v>
       </c>
       <c r="DM3" s="0" t="n">
-        <v>73.25</v>
+        <v>162.87</v>
       </c>
       <c r="DN3" s="0" t="n">
-        <v>17.91</v>
+        <v>83.85</v>
       </c>
       <c r="DO3" s="0" t="n">
-        <v>4.92</v>
+        <v>46.5</v>
       </c>
       <c r="DP3" s="0" t="n">
-        <v>22.84</v>
+        <v>130.36</v>
       </c>
       <c r="DQ3" s="0" t="n">
-        <v>61.01</v>
+        <v>72.38</v>
       </c>
       <c r="DR3" s="0" t="n">
-        <v>31.18</v>
+        <v>31.08</v>
       </c>
       <c r="DS3" s="0" t="n">
-        <v>44.7</v>
+        <v>76.43</v>
       </c>
       <c r="DT3" s="0" t="n">
-        <v>4.35</v>
+        <v>4.72</v>
       </c>
       <c r="DU3" s="0" t="n">
-        <v>53.08</v>
+        <v>70.77</v>
       </c>
       <c r="DV3" s="0" t="n">
-        <v>6.52</v>
+        <v>11.32</v>
       </c>
       <c r="DW3" s="0" t="n">
-        <v>2.17</v>
+        <v>5.66</v>
       </c>
       <c r="DX3" s="0" t="n">
-        <v>0.31</v>
+        <v>2.83</v>
       </c>
       <c r="DY3" s="0" t="n">
-        <v>2.48</v>
+        <v>8.49</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>E. Henriksson</t>
+          <t>M. Jalloh</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E4" s="0" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-06-30</t>
         </is>
       </c>
       <c r="H4" s="0" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>1265</v>
+        <v>2397</v>
       </c>
       <c r="J4" s="0" t="n">
         <v>0</v>
@@ -1725,48 +1725,48 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="0" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>100.0</v>
+        <v>91.67</v>
       </c>
       <c r="P4" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="Q4" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="R4" s="0" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="T4" s="0" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="U4" s="0" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V4" s="0" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="W4" s="0" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="X4" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="Y4" s="0" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="Z4" s="0" t="n">
         <v>100.0</v>
@@ -1781,19 +1781,19 @@
         <v>0.0</v>
       </c>
       <c r="AD4" s="0" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="AE4" s="0" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="AF4" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="AG4" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH4" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AI4" s="0" t="n">
         <v>0</v>
@@ -1802,7 +1802,7 @@
         <v>0.0</v>
       </c>
       <c r="AK4" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AL4" s="0" t="n">
         <v>0.0</v>
@@ -1859,13 +1859,13 @@
         <v>0.0</v>
       </c>
       <c r="BD4" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BE4" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="BF4" s="0" t="n">
-        <v>0.07</v>
+        <v>0.23</v>
       </c>
       <c r="BG4" s="0" t="n">
         <v>100.0</v>
@@ -1880,55 +1880,55 @@
         <v>0.0</v>
       </c>
       <c r="BK4" s="0" t="n">
-        <v>9.39</v>
+        <v>20.65</v>
       </c>
       <c r="BL4" s="0" t="n">
-        <v>0.0</v>
+        <v>0.23</v>
       </c>
       <c r="BM4" s="0" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="BN4" s="0" t="n">
-        <v>18.78</v>
+        <v>31.13</v>
       </c>
       <c r="BO4" s="0" t="n">
-        <v>77.65</v>
+        <v>80.46</v>
       </c>
       <c r="BP4" s="0" t="n">
-        <v>12.31</v>
+        <v>16.63</v>
       </c>
       <c r="BQ4" s="0" t="n">
-        <v>67.05</v>
+        <v>67.27</v>
       </c>
       <c r="BR4" s="0" t="n">
-        <v>0.0</v>
+        <v>0.08</v>
       </c>
       <c r="BS4" s="0" t="n">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="BT4" s="0" t="n">
-        <v>6.26</v>
+        <v>12.24</v>
       </c>
       <c r="BU4" s="0" t="n">
-        <v>98.86</v>
+        <v>96.32</v>
       </c>
       <c r="BV4" s="0" t="n">
-        <v>9.18</v>
+        <v>18.81</v>
       </c>
       <c r="BW4" s="0" t="n">
-        <v>97.67</v>
+        <v>97.01</v>
       </c>
       <c r="BX4" s="0" t="n">
-        <v>9.53</v>
+        <v>12.13</v>
       </c>
       <c r="BY4" s="0" t="n">
-        <v>58.96</v>
+        <v>56.04</v>
       </c>
       <c r="BZ4" s="0" t="n">
-        <v>37.89</v>
+        <v>32.97</v>
       </c>
       <c r="CA4" s="0" t="n">
-        <v>51.79</v>
+        <v>51.15</v>
       </c>
       <c r="CB4" s="0" t="n">
         <v>0.0</v>
@@ -1952,73 +1952,73 @@
         <v>0.0</v>
       </c>
       <c r="CI4" s="0" t="n">
-        <v>3.2</v>
+        <v>4.24</v>
       </c>
       <c r="CJ4" s="0" t="n">
-        <v>46.67</v>
+        <v>44.25</v>
       </c>
       <c r="CK4" s="0" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="CL4" s="0" t="n">
-        <v>25.0</v>
+        <v>12.5</v>
       </c>
       <c r="CM4" s="0" t="n">
-        <v>0.43</v>
+        <v>0.04</v>
       </c>
       <c r="CN4" s="0" t="n">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="CO4" s="0" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="CP4" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ4" s="0" t="n">
-        <v>7.4</v>
+        <v>9.05</v>
       </c>
       <c r="CR4" s="0" t="n">
-        <v>70.19</v>
+        <v>72.2</v>
       </c>
       <c r="CS4" s="0" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="CT4" s="0" t="n">
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
       <c r="CU4" s="0" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="CV4" s="0" t="n">
-        <v>3.91</v>
+        <v>3.72</v>
       </c>
       <c r="CW4" s="0" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CX4" s="0" t="n">
-        <v>76.36</v>
+        <v>74.75</v>
       </c>
       <c r="CY4" s="0" t="n">
-        <v>16.22</v>
+        <v>28.19</v>
       </c>
       <c r="CZ4" s="0" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="DA4" s="0" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="DB4" s="0" t="n">
-        <v>0.229</v>
+        <v>0.12</v>
       </c>
       <c r="DC4" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD4" s="0" t="n">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="DE4" s="0" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" s="0" t="inlineStr">
         <is>
@@ -2045,62 +2045,62 @@
         <v>0.0</v>
       </c>
       <c r="DL4" s="0" t="n">
-        <v>4017.5</v>
+        <v>6279.92</v>
       </c>
       <c r="DM4" s="0" t="n">
-        <v>64.95</v>
+        <v>197.4</v>
       </c>
       <c r="DN4" s="0" t="n">
-        <v>9.21</v>
+        <v>35.03</v>
       </c>
       <c r="DO4" s="0" t="n">
-        <v>3.44</v>
+        <v>9.29</v>
       </c>
       <c r="DP4" s="0" t="n">
-        <v>12.65</v>
+        <v>44.32</v>
       </c>
       <c r="DQ4" s="0" t="n">
-        <v>44.64</v>
+        <v>69.78</v>
       </c>
       <c r="DR4" s="0" t="n">
-        <v>29.21</v>
+        <v>31.07</v>
       </c>
       <c r="DS4" s="0" t="n">
-        <v>40.3</v>
+        <v>69.3</v>
       </c>
       <c r="DT4" s="0" t="n">
-        <v>3.0</v>
+        <v>7.91</v>
       </c>
       <c r="DU4" s="0" t="n">
-        <v>47.59</v>
+        <v>82.79</v>
       </c>
       <c r="DV4" s="0" t="n">
-        <v>3.0</v>
+        <v>6.98</v>
       </c>
       <c r="DW4" s="0" t="n">
-        <v>1.71</v>
+        <v>4.19</v>
       </c>
       <c r="DX4" s="0" t="n">
-        <v>0.43</v>
+        <v>0.93</v>
       </c>
       <c r="DY4" s="0" t="n">
-        <v>2.14</v>
+        <v>5.12</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>Otso Virtanen</t>
+          <t>Miguel Santos</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -2109,21 +2109,21 @@
         </is>
       </c>
       <c r="E5" s="0" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="H5" s="0" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>416</v>
+        <v>2277</v>
       </c>
       <c r="J5" s="0" t="n">
         <v>0</v>
@@ -2138,19 +2138,19 @@
         <v>0.0</v>
       </c>
       <c r="N5" s="0" t="n">
-        <v>1.73</v>
+        <v>0.55</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>87.5</v>
+        <v>78.57</v>
       </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="Q5" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="R5" s="0" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="T5" s="0" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="U5" s="0" t="inlineStr">
         <is>
@@ -2170,43 +2170,43 @@
         </is>
       </c>
       <c r="V5" s="0" t="n">
-        <v>3.25</v>
+        <v>0.91</v>
       </c>
       <c r="W5" s="0" t="n">
-        <v>0.43</v>
+        <v>0.0</v>
       </c>
       <c r="X5" s="0" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y5" s="0" t="n">
-        <v>0.65</v>
+        <v>0.12</v>
       </c>
       <c r="Z5" s="0" t="n">
-        <v>100.0</v>
+        <v>66.67</v>
       </c>
       <c r="AA5" s="0" t="n">
-        <v>0.22</v>
+        <v>0.0</v>
       </c>
       <c r="AB5" s="0" t="n">
-        <v>0.25</v>
+        <v>0.0</v>
       </c>
       <c r="AC5" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>2.6</v>
+        <v>0.91</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>2.95</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="AG5" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AI5" s="0" t="n">
         <v>0</v>
@@ -2278,10 +2278,10 @@
         <v>0.0</v>
       </c>
       <c r="BF5" s="0" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="BG5" s="0" t="n">
-        <v>100.0</v>
+        <v>71.43</v>
       </c>
       <c r="BH5" s="0" t="n">
         <v>0.0</v>
@@ -2293,25 +2293,25 @@
         <v>0.0</v>
       </c>
       <c r="BK5" s="0" t="n">
-        <v>17.31</v>
+        <v>15.45</v>
       </c>
       <c r="BL5" s="0" t="n">
-        <v>0.0</v>
+        <v>0.2</v>
       </c>
       <c r="BM5" s="0" t="n">
         <v>0.43</v>
       </c>
       <c r="BN5" s="0" t="n">
-        <v>27.69</v>
+        <v>28.97</v>
       </c>
       <c r="BO5" s="0" t="n">
-        <v>85.16</v>
+        <v>83.63</v>
       </c>
       <c r="BP5" s="0" t="n">
-        <v>10.17</v>
+        <v>15.49</v>
       </c>
       <c r="BQ5" s="0" t="n">
-        <v>63.83</v>
+        <v>73.72</v>
       </c>
       <c r="BR5" s="0" t="n">
         <v>0.0</v>
@@ -2320,28 +2320,28 @@
         <v>0.0</v>
       </c>
       <c r="BT5" s="0" t="n">
-        <v>14.28</v>
+        <v>12.53</v>
       </c>
       <c r="BU5" s="0" t="n">
-        <v>96.97</v>
+        <v>94.95</v>
       </c>
       <c r="BV5" s="0" t="n">
-        <v>20.77</v>
+        <v>19.01</v>
       </c>
       <c r="BW5" s="0" t="n">
-        <v>98.96</v>
+        <v>94.59</v>
       </c>
       <c r="BX5" s="0" t="n">
-        <v>6.92</v>
+        <v>9.96</v>
       </c>
       <c r="BY5" s="0" t="n">
-        <v>43.75</v>
+        <v>62.7</v>
       </c>
       <c r="BZ5" s="0" t="n">
-        <v>24.26</v>
+        <v>30.8</v>
       </c>
       <c r="CA5" s="0" t="n">
-        <v>47.57</v>
+        <v>45.43</v>
       </c>
       <c r="CB5" s="0" t="n">
         <v>0.0</v>
@@ -2365,13 +2365,13 @@
         <v>0.0</v>
       </c>
       <c r="CI5" s="0" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="CJ5" s="0" t="n">
-        <v>44.44</v>
+        <v>44.64</v>
       </c>
       <c r="CK5" s="0" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="CL5" s="0" t="n">
         <v>0.0</v>
@@ -2389,49 +2389,49 @@
         <v>0.0</v>
       </c>
       <c r="CQ5" s="0" t="n">
-        <v>4.54</v>
+        <v>7.55</v>
       </c>
       <c r="CR5" s="0" t="n">
-        <v>52.38</v>
+        <v>67.02</v>
       </c>
       <c r="CS5" s="0" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="CT5" s="0" t="n">
-        <v>2.38</v>
+        <v>0.95</v>
       </c>
       <c r="CU5" s="0" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="CV5" s="0" t="n">
-        <v>5.41</v>
+        <v>3.64</v>
       </c>
       <c r="CW5" s="0" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CX5" s="0" t="n">
-        <v>56.0</v>
+        <v>73.91</v>
       </c>
       <c r="CY5" s="0" t="n">
-        <v>9.52</v>
+        <v>31.1</v>
       </c>
       <c r="CZ5" s="0" t="n">
-        <v>2.06</v>
+        <v>1.23</v>
       </c>
       <c r="DA5" s="0" t="n">
-        <v>-1.48</v>
+        <v>7.1</v>
       </c>
       <c r="DB5" s="0" t="n">
-        <v>-0.32</v>
+        <v>0.281</v>
       </c>
       <c r="DC5" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD5" s="0" t="n">
-        <v>3.25</v>
+        <v>1.82</v>
       </c>
       <c r="DE5" s="0" t="n">
-        <v>0.65</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" s="0" t="inlineStr">
         <is>
@@ -2458,46 +2458,46 @@
         <v>0.0</v>
       </c>
       <c r="DL5" s="0" t="n">
-        <v>6514.08</v>
+        <v>6016.51</v>
       </c>
       <c r="DM5" s="0" t="n">
-        <v>162.87</v>
+        <v>92.36</v>
       </c>
       <c r="DN5" s="0" t="n">
-        <v>83.85</v>
+        <v>26.87</v>
       </c>
       <c r="DO5" s="0" t="n">
-        <v>46.5</v>
+        <v>1.55</v>
       </c>
       <c r="DP5" s="0" t="n">
-        <v>130.36</v>
+        <v>28.42</v>
       </c>
       <c r="DQ5" s="0" t="n">
-        <v>72.38</v>
+        <v>66.85</v>
       </c>
       <c r="DR5" s="0" t="n">
-        <v>31.08</v>
+        <v>26.39</v>
       </c>
       <c r="DS5" s="0" t="n">
-        <v>76.43</v>
+        <v>54.63</v>
       </c>
       <c r="DT5" s="0" t="n">
-        <v>4.72</v>
+        <v>3.83</v>
       </c>
       <c r="DU5" s="0" t="n">
-        <v>70.77</v>
+        <v>58.46</v>
       </c>
       <c r="DV5" s="0" t="n">
-        <v>11.32</v>
+        <v>5.11</v>
       </c>
       <c r="DW5" s="0" t="n">
-        <v>5.66</v>
+        <v>3.51</v>
       </c>
       <c r="DX5" s="0" t="n">
-        <v>2.83</v>
+        <v>0.0</v>
       </c>
       <c r="DY5" s="0" t="n">
-        <v>8.49</v>
+        <v>3.51</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="6">
@@ -2533,16 +2533,16 @@
         </is>
       </c>
       <c r="H6" s="0" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>1038</v>
+        <v>1985</v>
       </c>
       <c r="J6" s="0" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
       <c r="L6" s="0" t="n">
         <v>0</v>
@@ -2551,10 +2551,10 @@
         <v>0.0</v>
       </c>
       <c r="N6" s="0" t="n">
-        <v>0.95</v>
+        <v>0.63</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>81.82</v>
+        <v>78.57</v>
       </c>
       <c r="P6" s="0" t="inlineStr">
         <is>
@@ -2583,19 +2583,19 @@
         </is>
       </c>
       <c r="V6" s="0" t="n">
-        <v>1.13</v>
+        <v>0.82</v>
       </c>
       <c r="W6" s="0" t="n">
         <v>0.09</v>
       </c>
       <c r="X6" s="0" t="n">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="Y6" s="0" t="n">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="Z6" s="0" t="n">
-        <v>71.43</v>
+        <v>77.78</v>
       </c>
       <c r="AA6" s="0" t="n">
         <v>0.0</v>
@@ -2607,19 +2607,19 @@
         <v>0.0</v>
       </c>
       <c r="AD6" s="0" t="n">
-        <v>1.04</v>
+        <v>0.77</v>
       </c>
       <c r="AE6" s="0" t="n">
-        <v>1.24</v>
+        <v>0.91</v>
       </c>
       <c r="AF6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="AG6" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6" s="0" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AI6" s="0" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0.0</v>
       </c>
       <c r="AR6" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="AT6" s="0" t="n">
         <v>0.0</v>
@@ -2691,7 +2691,7 @@
         <v>0.0</v>
       </c>
       <c r="BF6" s="0" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="BG6" s="0" t="n">
         <v>100.0</v>
@@ -2706,55 +2706,55 @@
         <v>0.0</v>
       </c>
       <c r="BK6" s="0" t="n">
-        <v>13.96</v>
+        <v>15.05</v>
       </c>
       <c r="BL6" s="0" t="n">
-        <v>0.0</v>
+        <v>0.09</v>
       </c>
       <c r="BM6" s="0" t="n">
-        <v>0.43</v>
+        <v>0.32</v>
       </c>
       <c r="BN6" s="0" t="n">
-        <v>22.89</v>
+        <v>26.34</v>
       </c>
       <c r="BO6" s="0" t="n">
-        <v>87.12</v>
+        <v>83.99</v>
       </c>
       <c r="BP6" s="0" t="n">
-        <v>10.4</v>
+        <v>11.92</v>
       </c>
       <c r="BQ6" s="0" t="n">
-        <v>72.5</v>
+        <v>68.82</v>
       </c>
       <c r="BR6" s="0" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="BS6" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="BT6" s="0" t="n">
-        <v>9.71</v>
+        <v>12.11</v>
       </c>
       <c r="BU6" s="0" t="n">
-        <v>99.11</v>
+        <v>96.63</v>
       </c>
       <c r="BV6" s="0" t="n">
-        <v>16.99</v>
+        <v>19.13</v>
       </c>
       <c r="BW6" s="0" t="n">
-        <v>97.96</v>
+        <v>96.68</v>
       </c>
       <c r="BX6" s="0" t="n">
-        <v>5.9</v>
+        <v>7.12</v>
       </c>
       <c r="BY6" s="0" t="n">
-        <v>55.88</v>
+        <v>50.96</v>
       </c>
       <c r="BZ6" s="0" t="n">
-        <v>25.04</v>
+        <v>25.63</v>
       </c>
       <c r="CA6" s="0" t="n">
-        <v>47.36</v>
+        <v>46.92</v>
       </c>
       <c r="CB6" s="0" t="n">
         <v>0.0</v>
@@ -2778,10 +2778,10 @@
         <v>0.0</v>
       </c>
       <c r="CI6" s="0" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="CJ6" s="0" t="n">
-        <v>33.33</v>
+        <v>20.0</v>
       </c>
       <c r="CK6" s="0" t="n">
         <v>0.0</v>
@@ -2802,49 +2802,49 @@
         <v>0.0</v>
       </c>
       <c r="CQ6" s="0" t="n">
-        <v>5.2</v>
+        <v>6.62</v>
       </c>
       <c r="CR6" s="0" t="n">
-        <v>61.67</v>
+        <v>50.68</v>
       </c>
       <c r="CS6" s="0" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="CT6" s="0" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="CU6" s="0" t="n">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="CV6" s="0" t="n">
-        <v>4.77</v>
+        <v>4.49</v>
       </c>
       <c r="CW6" s="0" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CX6" s="0" t="n">
-        <v>67.27</v>
+        <v>72.73</v>
       </c>
       <c r="CY6" s="0" t="n">
-        <v>17.91</v>
+        <v>28.39</v>
       </c>
       <c r="CZ6" s="0" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="DA6" s="0" t="n">
-        <v>-0.09</v>
+        <v>1.39</v>
       </c>
       <c r="DB6" s="0" t="n">
-        <v>-0.008</v>
+        <v>0.063</v>
       </c>
       <c r="DC6" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD6" s="0" t="n">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="DE6" s="0" t="n">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="DF6" s="0" t="inlineStr">
         <is>
@@ -2916,17 +2916,17 @@
     <row ht="12" customHeight="true" r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>M. Riikonen</t>
+          <t>E. Huuhtanen</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E7" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="F7" s="0" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>7</v>
-      </c>
       <c r="I7" s="0" t="n">
-        <v>672</v>
+        <v>2306</v>
       </c>
       <c r="J7" s="0" t="n">
         <v>0</v>
@@ -2964,10 +2964,10 @@
         <v>0.0</v>
       </c>
       <c r="N7" s="0" t="n">
-        <v>1.07</v>
+        <v>0.47</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="P7" s="0" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="S7" s="0" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="T7" s="0" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U7" s="0" t="inlineStr">
         <is>
@@ -2996,268 +2996,268 @@
         </is>
       </c>
       <c r="V7" s="0" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="W7" s="0" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="X7" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="Y7" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z7" s="0" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="AA7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD7" s="0" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="AE7" s="0" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AI7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AT7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF7" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BG7" s="0" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BH7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI7" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BJ7" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BK7" s="0" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="BL7" s="0" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BM7" s="0" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BN7" s="0" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="BO7" s="0" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="BP7" s="0" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="BQ7" s="0" t="n">
+        <v>76.53</v>
+      </c>
+      <c r="BR7" s="0" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BS7" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BT7" s="0" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="BU7" s="0" t="n">
+        <v>96.54</v>
+      </c>
+      <c r="BV7" s="0" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="BW7" s="0" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="BX7" s="0" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="BY7" s="0" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="BZ7" s="0" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="CA7" s="0" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="CB7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI7" s="0" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="CJ7" s="0" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="CK7" s="0" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CL7" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CM7" s="0" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="CN7" s="0" t="n">
         <v>50.0</v>
       </c>
-      <c r="Y7" s="0" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="Z7" s="0" t="n">
-        <v>60.0</v>
-      </c>
-      <c r="AA7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD7" s="0" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE7" s="0" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AL7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AO7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AP7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AR7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AT7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AU7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AV7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AW7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AX7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AY7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AZ7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BA7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BB7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BC7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BD7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BE7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BF7" s="0" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BG7" s="0" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="BH7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BI7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BK7" s="0" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="BL7" s="0" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BM7" s="0" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BN7" s="0" t="n">
-        <v>24.24</v>
-      </c>
-      <c r="BO7" s="0" t="n">
-        <v>83.43</v>
-      </c>
-      <c r="BP7" s="0" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="BQ7" s="0" t="n">
-        <v>70.1</v>
-      </c>
-      <c r="BR7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT7" s="0" t="n">
-        <v>9.64</v>
-      </c>
-      <c r="BU7" s="0" t="n">
-        <v>98.61</v>
-      </c>
-      <c r="BV7" s="0" t="n">
-        <v>14.87</v>
-      </c>
-      <c r="BW7" s="0" t="n">
-        <v>99.1</v>
-      </c>
-      <c r="BX7" s="0" t="n">
-        <v>9.38</v>
-      </c>
-      <c r="BY7" s="0" t="n">
-        <v>58.57</v>
-      </c>
-      <c r="BZ7" s="0" t="n">
-        <v>30.96</v>
-      </c>
-      <c r="CA7" s="0" t="n">
-        <v>49.64</v>
-      </c>
-      <c r="CB7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CC7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CD7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CE7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CF7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CG7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CH7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CI7" s="0" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CJ7" s="0" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="CK7" s="0" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="CL7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CM7" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CN7" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="CO7" s="0" t="n">
-        <v>0.13</v>
+        <v>0.0</v>
       </c>
       <c r="CP7" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ7" s="0" t="n">
-        <v>6.83</v>
+        <v>8.51</v>
       </c>
       <c r="CR7" s="0" t="n">
-        <v>78.43</v>
+        <v>63.76</v>
       </c>
       <c r="CS7" s="0" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="CT7" s="0" t="n">
-        <v>2.01</v>
+        <v>0.7</v>
       </c>
       <c r="CU7" s="0" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="CV7" s="0" t="n">
-        <v>6.96</v>
+        <v>2.42</v>
       </c>
       <c r="CW7" s="0" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CX7" s="0" t="n">
-        <v>71.15</v>
+        <v>70.97</v>
       </c>
       <c r="CY7" s="0" t="n">
-        <v>19.02</v>
+        <v>15.9</v>
       </c>
       <c r="CZ7" s="0" t="n">
-        <v>2.55</v>
+        <v>0.62</v>
       </c>
       <c r="DA7" s="0" t="n">
-        <v>4.02</v>
+        <v>-2.1</v>
       </c>
       <c r="DB7" s="0" t="n">
-        <v>0.538</v>
+        <v>-0.082</v>
       </c>
       <c r="DC7" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD7" s="0" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="DE7" s="0" t="n">
-        <v>0.67</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" s="0" t="inlineStr">
         <is>
@@ -3284,62 +3284,62 @@
         <v>0.0</v>
       </c>
       <c r="DL7" s="0" t="n">
-        <v>5407.3</v>
+        <v>5735.61</v>
       </c>
       <c r="DM7" s="0" t="n">
-        <v>90.82</v>
+        <v>124.67</v>
       </c>
       <c r="DN7" s="0" t="n">
-        <v>11.57</v>
+        <v>22.04</v>
       </c>
       <c r="DO7" s="0" t="n">
-        <v>4.15</v>
+        <v>4.39</v>
       </c>
       <c r="DP7" s="0" t="n">
-        <v>15.71</v>
+        <v>26.42</v>
       </c>
       <c r="DQ7" s="0" t="n">
-        <v>60.08</v>
+        <v>63.73</v>
       </c>
       <c r="DR7" s="0" t="n">
-        <v>26.15</v>
+        <v>28.99</v>
       </c>
       <c r="DS7" s="0" t="n">
-        <v>76.16</v>
+        <v>82.5</v>
       </c>
       <c r="DT7" s="0" t="n">
-        <v>5.78</v>
+        <v>10.43</v>
       </c>
       <c r="DU7" s="0" t="n">
-        <v>69.42</v>
+        <v>86.23</v>
       </c>
       <c r="DV7" s="0" t="n">
-        <v>3.86</v>
+        <v>10.43</v>
       </c>
       <c r="DW7" s="0" t="n">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="DX7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.19</v>
       </c>
       <c r="DY7" s="0" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>A. Craninx</t>
+          <t>S. Vits</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -3351,7 +3351,7 @@
         <v>30</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="H8" s="0" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>1073</v>
+        <v>2372</v>
       </c>
       <c r="J8" s="0" t="n">
         <v>0</v>
@@ -3371,25 +3371,25 @@
         <v>0.0</v>
       </c>
       <c r="L8" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="0" t="n">
-        <v>0.23</v>
+        <v>0.0</v>
       </c>
       <c r="N8" s="0" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>92.31</v>
+        <v>82.14</v>
       </c>
       <c r="P8" s="0" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="Q8" s="0" t="inlineStr">
         <is>
-          <t>Spain, Belgium</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="R8" s="0" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="S8" s="0" t="n">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="T8" s="0" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" s="0" t="inlineStr">
         <is>
@@ -3409,19 +3409,19 @@
         </is>
       </c>
       <c r="V8" s="0" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="W8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.11</v>
       </c>
       <c r="X8" s="0" t="n">
-        <v>0.0</v>
+        <v>66.67</v>
       </c>
       <c r="Y8" s="0" t="n">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="Z8" s="0" t="n">
-        <v>85.71</v>
+        <v>87.5</v>
       </c>
       <c r="AA8" s="0" t="n">
         <v>0.0</v>
@@ -3433,19 +3433,19 @@
         <v>0.0</v>
       </c>
       <c r="AD8" s="0" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="AE8" s="0" t="n">
-        <v>1.64</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" s="0" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AG8" s="0" t="n">
         <v>1</v>
       </c>
       <c r="AH8" s="0" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AI8" s="0" t="n">
         <v>0</v>
@@ -3454,7 +3454,7 @@
         <v>0.0</v>
       </c>
       <c r="AK8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AL8" s="0" t="n">
         <v>0.0</v>
@@ -3487,7 +3487,7 @@
         <v>0.0</v>
       </c>
       <c r="AV8" s="0" t="n">
-        <v>0.08</v>
+        <v>0.0</v>
       </c>
       <c r="AW8" s="0" t="n">
         <v>0.0</v>
@@ -3511,82 +3511,82 @@
         <v>0.0</v>
       </c>
       <c r="BD8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BE8" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="BF8" s="0" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="BG8" s="0" t="n">
-        <v>100.0</v>
+        <v>84.62</v>
       </c>
       <c r="BH8" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BI8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BJ8" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BK8" s="0" t="n">
-        <v>14.76</v>
+        <v>15.25</v>
       </c>
       <c r="BL8" s="0" t="n">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="BM8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="BN8" s="0" t="n">
-        <v>27.51</v>
+        <v>25.57</v>
       </c>
       <c r="BO8" s="0" t="n">
-        <v>75.61</v>
+        <v>73.74</v>
       </c>
       <c r="BP8" s="0" t="n">
-        <v>15.85</v>
+        <v>17.11</v>
       </c>
       <c r="BQ8" s="0" t="n">
-        <v>59.79</v>
+        <v>63.86</v>
       </c>
       <c r="BR8" s="0" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BS8" s="0" t="n">
-        <v>100.0</v>
+        <v>33.33</v>
       </c>
       <c r="BT8" s="0" t="n">
-        <v>10.07</v>
+        <v>7.82</v>
       </c>
       <c r="BU8" s="0" t="n">
-        <v>96.67</v>
+        <v>94.17</v>
       </c>
       <c r="BV8" s="0" t="n">
-        <v>15.77</v>
+        <v>12.52</v>
       </c>
       <c r="BW8" s="0" t="n">
-        <v>96.28</v>
+        <v>96.06</v>
       </c>
       <c r="BX8" s="0" t="n">
-        <v>11.66</v>
+        <v>12.98</v>
       </c>
       <c r="BY8" s="0" t="n">
-        <v>48.2</v>
+        <v>52.63</v>
       </c>
       <c r="BZ8" s="0" t="n">
-        <v>35.96</v>
+        <v>40.09</v>
       </c>
       <c r="CA8" s="0" t="n">
-        <v>54.86</v>
+        <v>55.13</v>
       </c>
       <c r="CB8" s="0" t="n">
-        <v>0.02</v>
+        <v>0.0</v>
       </c>
       <c r="CC8" s="0" t="n">
-        <v>0.08</v>
+        <v>0.0</v>
       </c>
       <c r="CD8" s="0" t="n">
         <v>0.0</v>
@@ -3601,76 +3601,76 @@
         <v>0.0</v>
       </c>
       <c r="CH8" s="0" t="n">
-        <v>0.08</v>
+        <v>0.0</v>
       </c>
       <c r="CI8" s="0" t="n">
-        <v>5.28</v>
+        <v>5.43</v>
       </c>
       <c r="CJ8" s="0" t="n">
-        <v>49.21</v>
+        <v>46.85</v>
       </c>
       <c r="CK8" s="0" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="CL8" s="0" t="n">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
       <c r="CM8" s="0" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="CN8" s="0" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
       <c r="CO8" s="0" t="n">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="CP8" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ8" s="0" t="n">
-        <v>8.39</v>
+        <v>9.68</v>
       </c>
       <c r="CR8" s="0" t="n">
-        <v>66.0</v>
+        <v>70.2</v>
       </c>
       <c r="CS8" s="0" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="CT8" s="0" t="n">
-        <v>0.75</v>
+        <v>1.82</v>
       </c>
       <c r="CU8" s="0" t="n">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="CV8" s="0" t="n">
-        <v>3.36</v>
+        <v>5.05</v>
       </c>
       <c r="CW8" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CX8" s="0" t="n">
-        <v>77.5</v>
+        <v>63.91</v>
       </c>
       <c r="CY8" s="0" t="n">
-        <v>11.68</v>
+        <v>43.79</v>
       </c>
       <c r="CZ8" s="0" t="n">
-        <v>0.98</v>
+        <v>1.66</v>
       </c>
       <c r="DA8" s="0" t="n">
-        <v>2.68</v>
+        <v>-4.21</v>
       </c>
       <c r="DB8" s="0" t="n">
-        <v>0.225</v>
+        <v>-0.16</v>
       </c>
       <c r="DC8" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD8" s="0" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="DE8" s="0" t="n">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="DF8" s="0" t="inlineStr">
         <is>
@@ -3697,62 +3697,62 @@
         <v>0.0</v>
       </c>
       <c r="DL8" s="0" t="n">
-        <v>4979.95</v>
+        <v>5690.37</v>
       </c>
       <c r="DM8" s="0" t="n">
-        <v>76.3</v>
+        <v>84.94</v>
       </c>
       <c r="DN8" s="0" t="n">
-        <v>13.12</v>
+        <v>27.78</v>
       </c>
       <c r="DO8" s="0" t="n">
-        <v>0.0</v>
+        <v>3.79</v>
       </c>
       <c r="DP8" s="0" t="n">
-        <v>13.12</v>
+        <v>31.57</v>
       </c>
       <c r="DQ8" s="0" t="n">
-        <v>55.33</v>
+        <v>63.23</v>
       </c>
       <c r="DR8" s="0" t="n">
-        <v>23.02</v>
+        <v>27.92</v>
       </c>
       <c r="DS8" s="0" t="n">
-        <v>65.43</v>
+        <v>52.62</v>
       </c>
       <c r="DT8" s="0" t="n">
-        <v>0.0</v>
+        <v>4.7</v>
       </c>
       <c r="DU8" s="0" t="n">
-        <v>54.21</v>
+        <v>64.37</v>
       </c>
       <c r="DV8" s="0" t="n">
-        <v>4.67</v>
+        <v>5.64</v>
       </c>
       <c r="DW8" s="0" t="n">
-        <v>1.87</v>
+        <v>3.29</v>
       </c>
       <c r="DX8" s="0" t="n">
-        <v>0.0</v>
+        <v>0.47</v>
       </c>
       <c r="DY8" s="0" t="n">
-        <v>1.87</v>
+        <v>3.76</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>R. Paunio</t>
+          <t>M. Marković</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="E9" s="0" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
@@ -3772,10 +3772,10 @@
         </is>
       </c>
       <c r="H9" s="0" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>1041</v>
+        <v>1888</v>
       </c>
       <c r="J9" s="0" t="n">
         <v>0</v>
@@ -3790,19 +3790,19 @@
         <v>0.0</v>
       </c>
       <c r="N9" s="0" t="n">
-        <v>0.17</v>
+        <v>1.0</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>50.0</v>
+        <v>80.95</v>
       </c>
       <c r="P9" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="Q9" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Croatia, Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="R9" s="0" t="inlineStr">
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="S9" s="0" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="T9" s="0" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U9" s="0" t="inlineStr">
         <is>
@@ -3822,49 +3822,49 @@
         </is>
       </c>
       <c r="V9" s="0" t="n">
-        <v>1.64</v>
+        <v>0.86</v>
       </c>
       <c r="W9" s="0" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="X9" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="Y9" s="0" t="n">
-        <v>0.0</v>
+        <v>0.48</v>
       </c>
       <c r="Z9" s="0" t="n">
-        <v>0.0</v>
+        <v>80.0</v>
       </c>
       <c r="AA9" s="0" t="n">
-        <v>0.09</v>
+        <v>0.0</v>
       </c>
       <c r="AB9" s="0" t="n">
-        <v>0.11</v>
+        <v>0.0</v>
       </c>
       <c r="AC9" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>1.56</v>
+        <v>0.81</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>2.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>0.09</v>
+        <v>0.0</v>
       </c>
       <c r="AG9" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" s="0" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="AI9" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="0" t="n">
-        <v>0.09</v>
+        <v>0.0</v>
       </c>
       <c r="AK9" s="0" t="n">
         <v>0.0</v>
@@ -3924,76 +3924,76 @@
         <v>0.0</v>
       </c>
       <c r="BD9" s="0" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="BE9" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BF9" s="0" t="n">
-        <v>0.09</v>
+        <v>0.38</v>
       </c>
       <c r="BG9" s="0" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="BH9" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI9" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BJ9" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK9" s="0" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="BL9" s="0" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BM9" s="0" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BN9" s="0" t="n">
+        <v>22.79</v>
+      </c>
+      <c r="BO9" s="0" t="n">
+        <v>90.38</v>
+      </c>
+      <c r="BP9" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BQ9" s="0" t="n">
+        <v>84.68</v>
+      </c>
+      <c r="BR9" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BS9" s="0" t="n">
         <v>100.0</v>
       </c>
-      <c r="BH9" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BI9" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ9" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BK9" s="0" t="n">
-        <v>17.38</v>
-      </c>
-      <c r="BL9" s="0" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM9" s="0" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BN9" s="0" t="n">
-        <v>29.65</v>
-      </c>
-      <c r="BO9" s="0" t="n">
-        <v>82.51</v>
-      </c>
-      <c r="BP9" s="0" t="n">
-        <v>14.96</v>
-      </c>
-      <c r="BQ9" s="0" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="BR9" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS9" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="BT9" s="0" t="n">
-        <v>12.62</v>
+        <v>10.49</v>
       </c>
       <c r="BU9" s="0" t="n">
-        <v>93.15</v>
+        <v>95.91</v>
       </c>
       <c r="BV9" s="0" t="n">
-        <v>18.41</v>
+        <v>18.11</v>
       </c>
       <c r="BW9" s="0" t="n">
-        <v>96.24</v>
+        <v>97.37</v>
       </c>
       <c r="BX9" s="0" t="n">
-        <v>11.15</v>
+        <v>4.67</v>
       </c>
       <c r="BY9" s="0" t="n">
-        <v>60.47</v>
+        <v>63.27</v>
       </c>
       <c r="BZ9" s="0" t="n">
-        <v>30.07</v>
+        <v>24.36</v>
       </c>
       <c r="CA9" s="0" t="n">
-        <v>45.41</v>
+        <v>43.51</v>
       </c>
       <c r="CB9" s="0" t="n">
         <v>0.0</v>
@@ -4017,73 +4017,73 @@
         <v>0.0</v>
       </c>
       <c r="CI9" s="0" t="n">
-        <v>2.85</v>
+        <v>0.72</v>
       </c>
       <c r="CJ9" s="0" t="n">
-        <v>60.61</v>
+        <v>53.33</v>
       </c>
       <c r="CK9" s="0" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="CL9" s="0" t="n">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="CM9" s="0" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="CN9" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CO9" s="0" t="n">
-        <v>0.09</v>
+        <v>0.0</v>
       </c>
       <c r="CP9" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ9" s="0" t="n">
-        <v>8.9</v>
+        <v>3.91</v>
       </c>
       <c r="CR9" s="0" t="n">
-        <v>63.11</v>
+        <v>60.98</v>
       </c>
       <c r="CS9" s="0" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CT9" s="0" t="n">
-        <v>1.47</v>
+        <v>0.95</v>
       </c>
       <c r="CU9" s="0" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="CV9" s="0" t="n">
-        <v>4.84</v>
+        <v>3.67</v>
       </c>
       <c r="CW9" s="0" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="CX9" s="0" t="n">
-        <v>69.64</v>
+        <v>74.03</v>
       </c>
       <c r="CY9" s="0" t="n">
-        <v>19.67</v>
+        <v>19.2</v>
       </c>
       <c r="CZ9" s="0" t="n">
-        <v>1.7</v>
+        <v>0.92</v>
       </c>
       <c r="DA9" s="0" t="n">
-        <v>2.67</v>
+        <v>-0.8</v>
       </c>
       <c r="DB9" s="0" t="n">
-        <v>0.231</v>
+        <v>-0.038</v>
       </c>
       <c r="DC9" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD9" s="0" t="n">
-        <v>1.3</v>
+        <v>2.0</v>
       </c>
       <c r="DE9" s="0" t="n">
-        <v>0.0</v>
+        <v>0.48</v>
       </c>
       <c r="DF9" s="0" t="inlineStr">
         <is>
@@ -4109,91 +4109,63 @@
       <c r="DK9" s="0" t="n">
         <v>0.0</v>
       </c>
-      <c r="DL9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DM9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DN9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DO9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DP9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DQ9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DR9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DS9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DT9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DU9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DV9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DW9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DX9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DY9" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="DL9" s="0" t="n">
+        <v>5491.34</v>
+      </c>
+      <c r="DM9" s="0" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="DN9" s="0" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="DO9" s="0" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DP9" s="0" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="DQ9" s="0" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="DR9" s="0" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="DS9" s="0" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="DT9" s="0" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="DU9" s="0" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="DV9" s="0" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="DW9" s="0" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DX9" s="0" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DY9" s="0" t="n">
+        <v>2.48</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>E. Huuhtanen</t>
+          <t>M. Riikonen</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
@@ -4202,10 +4174,10 @@
         </is>
       </c>
       <c r="E10" s="0" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
@@ -4213,10 +4185,10 @@
         </is>
       </c>
       <c r="H10" s="0" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>1453</v>
+        <v>770</v>
       </c>
       <c r="J10" s="0" t="n">
         <v>0</v>
@@ -4231,10 +4203,10 @@
         <v>0.0</v>
       </c>
       <c r="N10" s="0" t="n">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="O10" s="0" t="n">
-        <v>75.0</v>
+        <v>50.0</v>
       </c>
       <c r="P10" s="0" t="inlineStr">
         <is>
@@ -4252,10 +4224,10 @@
         </is>
       </c>
       <c r="S10" s="0" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="T10" s="0" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="U10" s="0" t="inlineStr">
         <is>
@@ -4263,19 +4235,19 @@
         </is>
       </c>
       <c r="V10" s="0" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W10" s="0" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="X10" s="0" t="n">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="Y10" s="0" t="n">
-        <v>0.19</v>
+        <v>0.82</v>
       </c>
       <c r="Z10" s="0" t="n">
-        <v>66.67</v>
+        <v>42.86</v>
       </c>
       <c r="AA10" s="0" t="n">
         <v>0.0</v>
@@ -4287,19 +4259,19 @@
         <v>0.0</v>
       </c>
       <c r="AD10" s="0" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" s="0" t="n">
-        <v>1.72</v>
+        <v>1.32</v>
       </c>
       <c r="AF10" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="AG10" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" s="0" t="n">
-        <v>0.06</v>
+        <v>0.0</v>
       </c>
       <c r="AI10" s="0" t="n">
         <v>0</v>
@@ -4374,7 +4346,7 @@
         <v>0.12</v>
       </c>
       <c r="BG10" s="0" t="n">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="BH10" s="0" t="n">
         <v>0.0</v>
@@ -4386,25 +4358,25 @@
         <v>0.0</v>
       </c>
       <c r="BK10" s="0" t="n">
-        <v>32.52</v>
+        <v>13.68</v>
       </c>
       <c r="BL10" s="0" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="BM10" s="0" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="BN10" s="0" t="n">
-        <v>43.3</v>
+        <v>23.38</v>
       </c>
       <c r="BO10" s="0" t="n">
-        <v>88.41</v>
+        <v>81.5</v>
       </c>
       <c r="BP10" s="0" t="n">
-        <v>22.05</v>
+        <v>12.86</v>
       </c>
       <c r="BQ10" s="0" t="n">
-        <v>79.78</v>
+        <v>69.09</v>
       </c>
       <c r="BR10" s="0" t="n">
         <v>0.0</v>
@@ -4413,28 +4385,28 @@
         <v>0.0</v>
       </c>
       <c r="BT10" s="0" t="n">
-        <v>19.45</v>
+        <v>9.12</v>
       </c>
       <c r="BU10" s="0" t="n">
-        <v>97.45</v>
+        <v>96.15</v>
       </c>
       <c r="BV10" s="0" t="n">
-        <v>32.64</v>
+        <v>14.26</v>
       </c>
       <c r="BW10" s="0" t="n">
-        <v>98.67</v>
+        <v>97.54</v>
       </c>
       <c r="BX10" s="0" t="n">
-        <v>10.65</v>
+        <v>9.12</v>
       </c>
       <c r="BY10" s="0" t="n">
-        <v>56.98</v>
+        <v>56.41</v>
       </c>
       <c r="BZ10" s="0" t="n">
-        <v>27.12</v>
+        <v>31.3</v>
       </c>
       <c r="CA10" s="0" t="n">
-        <v>49.0</v>
+        <v>49.15</v>
       </c>
       <c r="CB10" s="0" t="n">
         <v>0.0</v>
@@ -4458,10 +4430,10 @@
         <v>0.0</v>
       </c>
       <c r="CI10" s="0" t="n">
-        <v>3.47</v>
+        <v>2.69</v>
       </c>
       <c r="CJ10" s="0" t="n">
-        <v>58.93</v>
+        <v>39.13</v>
       </c>
       <c r="CK10" s="0" t="n">
         <v>0.12</v>
@@ -4470,61 +4442,61 @@
         <v>0.0</v>
       </c>
       <c r="CM10" s="0" t="n">
-        <v>0.37</v>
+        <v>0.0</v>
       </c>
       <c r="CN10" s="0" t="n">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="CO10" s="0" t="n">
-        <v>0.0</v>
+        <v>0.12</v>
       </c>
       <c r="CP10" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ10" s="0" t="n">
-        <v>8.05</v>
+        <v>6.9</v>
       </c>
       <c r="CR10" s="0" t="n">
-        <v>69.23</v>
+        <v>74.58</v>
       </c>
       <c r="CS10" s="0" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CT10" s="0" t="n">
-        <v>0.74</v>
+        <v>2.22</v>
       </c>
       <c r="CU10" s="0" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="CV10" s="0" t="n">
-        <v>2.35</v>
+        <v>7.25</v>
       </c>
       <c r="CW10" s="0" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CX10" s="0" t="n">
-        <v>68.42</v>
+        <v>69.35</v>
       </c>
       <c r="CY10" s="0" t="n">
-        <v>9.79</v>
+        <v>23.87</v>
       </c>
       <c r="CZ10" s="0" t="n">
-        <v>0.61</v>
+        <v>2.79</v>
       </c>
       <c r="DA10" s="0" t="n">
-        <v>-2.21</v>
+        <v>4.87</v>
       </c>
       <c r="DB10" s="0" t="n">
-        <v>-0.137</v>
+        <v>0.569</v>
       </c>
       <c r="DC10" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD10" s="0" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="DE10" s="0" t="n">
-        <v>0.19</v>
+        <v>0.82</v>
       </c>
       <c r="DF10" s="0" t="inlineStr">
         <is>
@@ -4551,62 +4523,62 @@
         <v>0.0</v>
       </c>
       <c r="DL10" s="0" t="n">
-        <v>6061.19</v>
+        <v>5407.3</v>
       </c>
       <c r="DM10" s="0" t="n">
-        <v>137.22</v>
+        <v>90.82</v>
       </c>
       <c r="DN10" s="0" t="n">
-        <v>24.74</v>
+        <v>11.57</v>
       </c>
       <c r="DO10" s="0" t="n">
-        <v>3.24</v>
+        <v>4.15</v>
       </c>
       <c r="DP10" s="0" t="n">
-        <v>27.98</v>
+        <v>15.71</v>
       </c>
       <c r="DQ10" s="0" t="n">
-        <v>67.35</v>
+        <v>60.08</v>
       </c>
       <c r="DR10" s="0" t="n">
-        <v>28.99</v>
+        <v>26.15</v>
       </c>
       <c r="DS10" s="0" t="n">
-        <v>69.94</v>
+        <v>76.16</v>
       </c>
       <c r="DT10" s="0" t="n">
-        <v>5.79</v>
+        <v>5.78</v>
       </c>
       <c r="DU10" s="0" t="n">
-        <v>76.19</v>
+        <v>69.42</v>
       </c>
       <c r="DV10" s="0" t="n">
-        <v>6.72</v>
+        <v>3.86</v>
       </c>
       <c r="DW10" s="0" t="n">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="DX10" s="0" t="n">
-        <v>0.23</v>
+        <v>0.0</v>
       </c>
       <c r="DY10" s="0" t="n">
-        <v>3.47</v>
+        <v>2.89</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>Miguel Santos</t>
+          <t>A. Craninx</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Panionios</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -4615,21 +4587,21 @@
         </is>
       </c>
       <c r="E11" s="0" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2027-06-30</t>
         </is>
       </c>
       <c r="H11" s="0" t="n">
         <v>13</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>1241</v>
+        <v>1268</v>
       </c>
       <c r="J11" s="0" t="n">
         <v>0</v>
@@ -4638,25 +4610,25 @@
         <v>0.0</v>
       </c>
       <c r="L11" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="0" t="n">
-        <v>0.0</v>
+        <v>0.23</v>
       </c>
       <c r="N11" s="0" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>75.0</v>
+        <v>93.33</v>
       </c>
       <c r="P11" s="0" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="Q11" s="0" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Spain, Belgium</t>
         </is>
       </c>
       <c r="R11" s="0" t="inlineStr">
@@ -4665,10 +4637,10 @@
         </is>
       </c>
       <c r="S11" s="0" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="T11" s="0" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="U11" s="0" t="inlineStr">
         <is>
@@ -4676,7 +4648,7 @@
         </is>
       </c>
       <c r="V11" s="0" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="W11" s="0" t="n">
         <v>0.0</v>
@@ -4685,10 +4657,10 @@
         <v>0.0</v>
       </c>
       <c r="Y11" s="0" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="Z11" s="0" t="n">
-        <v>66.67</v>
+        <v>85.71</v>
       </c>
       <c r="AA11" s="0" t="n">
         <v>0.0</v>
@@ -4697,22 +4669,22 @@
         <v>0.0</v>
       </c>
       <c r="AC11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD11" s="0" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE11" s="0" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF11" s="0" t="n">
         <v>0.07</v>
       </c>
-      <c r="AD11" s="0" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE11" s="0" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF11" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="AG11" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" s="0" t="n">
-        <v>0.0</v>
+        <v>0.07</v>
       </c>
       <c r="AI11" s="0" t="n">
         <v>0</v>
@@ -4754,7 +4726,7 @@
         <v>0.0</v>
       </c>
       <c r="AV11" s="0" t="n">
-        <v>0.0</v>
+        <v>0.07</v>
       </c>
       <c r="AW11" s="0" t="n">
         <v>0.0</v>
@@ -4784,76 +4756,76 @@
         <v>0.0</v>
       </c>
       <c r="BF11" s="0" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="BG11" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BH11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BJ11" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK11" s="0" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="BL11" s="0" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BM11" s="0" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BN11" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="BO11" s="0" t="n">
+        <v>76.17</v>
+      </c>
+      <c r="BP11" s="0" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="BQ11" s="0" t="n">
         <v>60.0</v>
       </c>
-      <c r="BH11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BI11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BJ11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BK11" s="0" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="BL11" s="0" t="n">
+      <c r="BR11" s="0" t="n">
         <v>0.07</v>
       </c>
-      <c r="BM11" s="0" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN11" s="0" t="n">
-        <v>28.07</v>
-      </c>
-      <c r="BO11" s="0" t="n">
-        <v>82.69</v>
-      </c>
-      <c r="BP11" s="0" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="BQ11" s="0" t="n">
-        <v>70.59</v>
-      </c>
-      <c r="BR11" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="BS11" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="BT11" s="0" t="n">
-        <v>12.4</v>
+        <v>10.36</v>
       </c>
       <c r="BU11" s="0" t="n">
-        <v>95.91</v>
+        <v>97.26</v>
       </c>
       <c r="BV11" s="0" t="n">
-        <v>18.35</v>
+        <v>15.83</v>
       </c>
       <c r="BW11" s="0" t="n">
-        <v>94.47</v>
+        <v>96.41</v>
       </c>
       <c r="BX11" s="0" t="n">
-        <v>9.72</v>
+        <v>11.5</v>
       </c>
       <c r="BY11" s="0" t="n">
-        <v>60.45</v>
+        <v>48.77</v>
       </c>
       <c r="BZ11" s="0" t="n">
-        <v>30.22</v>
+        <v>35.98</v>
       </c>
       <c r="CA11" s="0" t="n">
-        <v>44.25</v>
+        <v>54.94</v>
       </c>
       <c r="CB11" s="0" t="n">
-        <v>0.0</v>
+        <v>0.02</v>
       </c>
       <c r="CC11" s="0" t="n">
-        <v>0.0</v>
+        <v>0.07</v>
       </c>
       <c r="CD11" s="0" t="n">
         <v>0.0</v>
@@ -4868,76 +4840,76 @@
         <v>0.0</v>
       </c>
       <c r="CH11" s="0" t="n">
-        <v>0.0</v>
+        <v>0.07</v>
       </c>
       <c r="CI11" s="0" t="n">
-        <v>1.96</v>
+        <v>5.32</v>
       </c>
       <c r="CJ11" s="0" t="n">
-        <v>29.63</v>
+        <v>48.0</v>
       </c>
       <c r="CK11" s="0" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CL11" s="0" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="CM11" s="0" t="n">
         <v>0.07</v>
       </c>
-      <c r="CL11" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CM11" s="0" t="n">
-        <v>0.0</v>
-      </c>
       <c r="CN11" s="0" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="CO11" s="0" t="n">
-        <v>0.0</v>
+        <v>0.21</v>
       </c>
       <c r="CP11" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ11" s="0" t="n">
-        <v>6.82</v>
+        <v>8.16</v>
       </c>
       <c r="CR11" s="0" t="n">
-        <v>65.96</v>
+        <v>66.96</v>
       </c>
       <c r="CS11" s="0" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CT11" s="0" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="CU11" s="0" t="n">
         <v>44</v>
       </c>
       <c r="CV11" s="0" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="CW11" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CX11" s="0" t="n">
-        <v>77.27</v>
+        <v>75.0</v>
       </c>
       <c r="CY11" s="0" t="n">
-        <v>16.2</v>
+        <v>13.03</v>
       </c>
       <c r="CZ11" s="0" t="n">
-        <v>1.17</v>
+        <v>0.93</v>
       </c>
       <c r="DA11" s="0" t="n">
-        <v>6.2</v>
+        <v>2.03</v>
       </c>
       <c r="DB11" s="0" t="n">
-        <v>0.45</v>
+        <v>0.144</v>
       </c>
       <c r="DC11" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD11" s="0" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DE11" s="0" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="DF11" s="0" t="inlineStr">
         <is>
@@ -4964,62 +4936,62 @@
         <v>0.0</v>
       </c>
       <c r="DL11" s="0" t="n">
-        <v>6016.51</v>
+        <v>4979.95</v>
       </c>
       <c r="DM11" s="0" t="n">
-        <v>92.36</v>
+        <v>76.3</v>
       </c>
       <c r="DN11" s="0" t="n">
-        <v>26.87</v>
+        <v>13.12</v>
       </c>
       <c r="DO11" s="0" t="n">
-        <v>1.55</v>
+        <v>0.0</v>
       </c>
       <c r="DP11" s="0" t="n">
-        <v>28.42</v>
+        <v>13.12</v>
       </c>
       <c r="DQ11" s="0" t="n">
-        <v>66.85</v>
+        <v>55.33</v>
       </c>
       <c r="DR11" s="0" t="n">
-        <v>26.39</v>
+        <v>23.02</v>
       </c>
       <c r="DS11" s="0" t="n">
-        <v>54.63</v>
+        <v>65.43</v>
       </c>
       <c r="DT11" s="0" t="n">
-        <v>3.83</v>
+        <v>0.0</v>
       </c>
       <c r="DU11" s="0" t="n">
-        <v>58.46</v>
+        <v>54.21</v>
       </c>
       <c r="DV11" s="0" t="n">
-        <v>5.11</v>
+        <v>4.67</v>
       </c>
       <c r="DW11" s="0" t="n">
-        <v>3.51</v>
+        <v>1.87</v>
       </c>
       <c r="DX11" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DY11" s="0" t="n">
-        <v>3.51</v>
+        <v>1.87</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>S. Vits</t>
+          <t>O. Maukonen</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -5028,7 +5000,7 @@
         </is>
       </c>
       <c r="E12" s="0" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>0</v>
@@ -5039,10 +5011,10 @@
         </is>
       </c>
       <c r="H12" s="0" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>1438</v>
+        <v>2295</v>
       </c>
       <c r="J12" s="0" t="n">
         <v>0</v>
@@ -5057,31 +5029,31 @@
         <v>0.0</v>
       </c>
       <c r="N12" s="0" t="n">
-        <v>1.31</v>
+        <v>0.98</v>
       </c>
       <c r="O12" s="0" t="n">
-        <v>80.95</v>
+        <v>88.0</v>
       </c>
       <c r="P12" s="0" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="Q12" s="0" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="R12" s="0" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="S12" s="0" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="T12" s="0" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="U12" s="0" t="inlineStr">
         <is>
@@ -5089,20 +5061,20 @@
         </is>
       </c>
       <c r="V12" s="0" t="n">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="W12" s="0" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="X12" s="0" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="Y12" s="0" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Z12" s="0" t="n">
         <v>100.0</v>
       </c>
-      <c r="Y12" s="0" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="Z12" s="0" t="n">
-        <v>83.33</v>
-      </c>
       <c r="AA12" s="0" t="n">
         <v>0.0</v>
       </c>
@@ -5113,19 +5085,19 @@
         <v>0.0</v>
       </c>
       <c r="AD12" s="0" t="n">
-        <v>1.0</v>
+        <v>0.59</v>
       </c>
       <c r="AE12" s="0" t="n">
-        <v>1.1</v>
+        <v>0.86</v>
       </c>
       <c r="AF12" s="0" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="AG12" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.08</v>
       </c>
       <c r="AI12" s="0" t="n">
         <v>0</v>
@@ -5197,70 +5169,70 @@
         <v>0.0</v>
       </c>
       <c r="BF12" s="0" t="n">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="BG12" s="0" t="n">
-        <v>80.0</v>
+        <v>88.89</v>
       </c>
       <c r="BH12" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BI12" s="0" t="n">
-        <v>0.06</v>
+        <v>0.0</v>
       </c>
       <c r="BJ12" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BK12" s="0" t="n">
-        <v>14.96</v>
+        <v>21.8</v>
       </c>
       <c r="BL12" s="0" t="n">
-        <v>0.38</v>
+        <v>0.24</v>
       </c>
       <c r="BM12" s="0" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="BN12" s="0" t="n">
-        <v>25.16</v>
+        <v>33.41</v>
       </c>
       <c r="BO12" s="0" t="n">
-        <v>72.39</v>
+        <v>81.34</v>
       </c>
       <c r="BP12" s="0" t="n">
-        <v>17.77</v>
+        <v>18.27</v>
       </c>
       <c r="BQ12" s="0" t="n">
-        <v>62.68</v>
+        <v>67.6</v>
       </c>
       <c r="BR12" s="0" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="BS12" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="BT12" s="0" t="n">
-        <v>6.82</v>
+        <v>14.12</v>
       </c>
       <c r="BU12" s="0" t="n">
-        <v>96.33</v>
+        <v>98.33</v>
       </c>
       <c r="BV12" s="0" t="n">
-        <v>11.02</v>
+        <v>21.02</v>
       </c>
       <c r="BW12" s="0" t="n">
-        <v>95.45</v>
+        <v>96.83</v>
       </c>
       <c r="BX12" s="0" t="n">
-        <v>14.02</v>
+        <v>12.39</v>
       </c>
       <c r="BY12" s="0" t="n">
-        <v>54.91</v>
+        <v>55.06</v>
       </c>
       <c r="BZ12" s="0" t="n">
-        <v>41.95</v>
+        <v>33.12</v>
       </c>
       <c r="CA12" s="0" t="n">
-        <v>56.21</v>
+        <v>52.05</v>
       </c>
       <c r="CB12" s="0" t="n">
         <v>0.0</v>
@@ -5272,7 +5244,7 @@
         <v>0.0</v>
       </c>
       <c r="CE12" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="CF12" s="0" t="n">
         <v>0.0</v>
@@ -5284,74 +5256,74 @@
         <v>0.0</v>
       </c>
       <c r="CI12" s="0" t="n">
-        <v>6.32</v>
+        <v>4.31</v>
       </c>
       <c r="CJ12" s="0" t="n">
-        <v>48.51</v>
+        <v>39.09</v>
       </c>
       <c r="CK12" s="0" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CL12" s="0" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="CM12" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CN12" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="CO12" s="0" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="CP12" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CQ12" s="0" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="CR12" s="0" t="n">
+        <v>69.13</v>
+      </c>
+      <c r="CS12" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT12" s="0" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="CU12" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="CV12" s="0" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CW12" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="CX12" s="0" t="n">
+        <v>74.42</v>
+      </c>
+      <c r="CY12" s="0" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="CZ12" s="0" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DA12" s="0" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="DB12" s="0" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="DC12" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD12" s="0" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DE12" s="0" t="n">
         <v>0.31</v>
       </c>
-      <c r="CL12" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CM12" s="0" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="CN12" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CO12" s="0" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="CP12" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CQ12" s="0" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="CR12" s="0" t="n">
-        <v>74.53</v>
-      </c>
-      <c r="CS12" s="0" t="n">
-        <v>32</v>
-      </c>
-      <c r="CT12" s="0" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="CU12" s="0" t="n">
-        <v>85</v>
-      </c>
-      <c r="CV12" s="0" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="CW12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="CX12" s="0" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="CY12" s="0" t="n">
-        <v>28.67</v>
-      </c>
-      <c r="CZ12" s="0" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DA12" s="0" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="DB12" s="0" t="n">
-        <v>-0.208</v>
-      </c>
-      <c r="DC12" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DD12" s="0" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="DE12" s="0" t="n">
-        <v>0.38</v>
-      </c>
       <c r="DF12" s="0" t="inlineStr">
         <is>
           <t/>
@@ -5377,62 +5349,62 @@
         <v>0.0</v>
       </c>
       <c r="DL12" s="0" t="n">
-        <v>5690.37</v>
+        <v>4747.67</v>
       </c>
       <c r="DM12" s="0" t="n">
-        <v>84.94</v>
+        <v>67.07</v>
       </c>
       <c r="DN12" s="0" t="n">
-        <v>27.78</v>
+        <v>13.78</v>
       </c>
       <c r="DO12" s="0" t="n">
-        <v>3.79</v>
+        <v>4.38</v>
       </c>
       <c r="DP12" s="0" t="n">
-        <v>31.57</v>
+        <v>18.15</v>
       </c>
       <c r="DQ12" s="0" t="n">
-        <v>63.23</v>
+        <v>52.75</v>
       </c>
       <c r="DR12" s="0" t="n">
-        <v>27.92</v>
+        <v>26.88</v>
       </c>
       <c r="DS12" s="0" t="n">
-        <v>52.62</v>
+        <v>52.78</v>
       </c>
       <c r="DT12" s="0" t="n">
-        <v>4.7</v>
+        <v>2.11</v>
       </c>
       <c r="DU12" s="0" t="n">
-        <v>64.37</v>
+        <v>52.78</v>
       </c>
       <c r="DV12" s="0" t="n">
-        <v>5.64</v>
+        <v>3.62</v>
       </c>
       <c r="DW12" s="0" t="n">
-        <v>3.29</v>
+        <v>1.51</v>
       </c>
       <c r="DX12" s="0" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="DY12" s="0" t="n">
-        <v>3.76</v>
+        <v>1.81</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>K. Lund</t>
+          <t>E. Henriksson</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -5441,21 +5413,21 @@
         </is>
       </c>
       <c r="E13" s="0" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2028-06-30</t>
         </is>
       </c>
       <c r="H13" s="0" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>676</v>
+        <v>2407</v>
       </c>
       <c r="J13" s="0" t="n">
         <v>0</v>
@@ -5470,31 +5442,31 @@
         <v>0.0</v>
       </c>
       <c r="N13" s="0" t="n">
-        <v>0.8</v>
+        <v>0.41</v>
       </c>
       <c r="O13" s="0" t="n">
-        <v>83.33</v>
+        <v>90.91</v>
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="Q13" s="0" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="R13" s="0" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>both</t>
         </is>
       </c>
       <c r="S13" s="0" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="T13" s="0" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="U13" s="0" t="inlineStr">
         <is>
@@ -5502,16 +5474,16 @@
         </is>
       </c>
       <c r="V13" s="0" t="n">
-        <v>2.0</v>
+        <v>0.64</v>
       </c>
       <c r="W13" s="0" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="X13" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="Y13" s="0" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="Z13" s="0" t="n">
         <v>100.0</v>
@@ -5526,19 +5498,19 @@
         <v>0.0</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>1.86</v>
+        <v>0.6</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>2.44</v>
+        <v>0.73</v>
       </c>
       <c r="AF13" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="AG13" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="0" t="n">
-        <v>0.13</v>
+        <v>0.0</v>
       </c>
       <c r="AI13" s="0" t="n">
         <v>0</v>
@@ -5610,40 +5582,40 @@
         <v>0.0</v>
       </c>
       <c r="BF13" s="0" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="BG13" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="BH13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BI13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BJ13" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BK13" s="0" t="n">
-        <v>15.04</v>
+        <v>12.0</v>
       </c>
       <c r="BL13" s="0" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="BM13" s="0" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
       </c>
       <c r="BN13" s="0" t="n">
-        <v>25.43</v>
+        <v>21.95</v>
       </c>
       <c r="BO13" s="0" t="n">
-        <v>80.63</v>
+        <v>78.53</v>
       </c>
       <c r="BP13" s="0" t="n">
         <v>14.51</v>
       </c>
       <c r="BQ13" s="0" t="n">
-        <v>69.72</v>
+        <v>69.33</v>
       </c>
       <c r="BR13" s="0" t="n">
         <v>0.0</v>
@@ -5652,28 +5624,28 @@
         <v>0.0</v>
       </c>
       <c r="BT13" s="0" t="n">
-        <v>9.85</v>
+        <v>7.03</v>
       </c>
       <c r="BU13" s="0" t="n">
-        <v>95.95</v>
+        <v>97.87</v>
       </c>
       <c r="BV13" s="0" t="n">
-        <v>16.51</v>
+        <v>11.52</v>
       </c>
       <c r="BW13" s="0" t="n">
-        <v>95.16</v>
+        <v>97.4</v>
       </c>
       <c r="BX13" s="0" t="n">
-        <v>8.92</v>
+        <v>10.36</v>
       </c>
       <c r="BY13" s="0" t="n">
-        <v>53.73</v>
+        <v>58.12</v>
       </c>
       <c r="BZ13" s="0" t="n">
-        <v>33.98</v>
+        <v>37.45</v>
       </c>
       <c r="CA13" s="0" t="n">
-        <v>50.82</v>
+        <v>51.54</v>
       </c>
       <c r="CB13" s="0" t="n">
         <v>0.0</v>
@@ -5697,183 +5669,155 @@
         <v>0.0</v>
       </c>
       <c r="CI13" s="0" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="CJ13" s="0" t="n">
-        <v>44.0</v>
+        <v>43.02</v>
       </c>
       <c r="CK13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.3</v>
       </c>
       <c r="CL13" s="0" t="n">
-        <v>0.0</v>
+        <v>12.5</v>
       </c>
       <c r="CM13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.22</v>
       </c>
       <c r="CN13" s="0" t="n">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
       <c r="CO13" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="CP13" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ13" s="0" t="n">
-        <v>6.39</v>
+        <v>8.11</v>
       </c>
       <c r="CR13" s="0" t="n">
-        <v>66.67</v>
+        <v>70.97</v>
       </c>
       <c r="CS13" s="0" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="CT13" s="0" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="CU13" s="0" t="n">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="CV13" s="0" t="n">
-        <v>7.59</v>
+        <v>4.08</v>
       </c>
       <c r="CW13" s="0" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CX13" s="0" t="n">
-        <v>75.44</v>
+        <v>75.23</v>
       </c>
       <c r="CY13" s="0" t="n">
-        <v>16.05</v>
+        <v>32.27</v>
       </c>
       <c r="CZ13" s="0" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DA13" s="0" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="DB13" s="0" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="DC13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD13" s="0" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DE13" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DF13" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DG13" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DH13" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DI13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DJ13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DL13" s="0" t="n">
+        <v>4017.5</v>
+      </c>
+      <c r="DM13" s="0" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="DN13" s="0" t="n">
+        <v>9.21</v>
+      </c>
+      <c r="DO13" s="0" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DP13" s="0" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="DQ13" s="0" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="DR13" s="0" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="DS13" s="0" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="DT13" s="0" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="DU13" s="0" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="DV13" s="0" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="DW13" s="0" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DX13" s="0" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DY13" s="0" t="n">
         <v>2.14</v>
-      </c>
-      <c r="DA13" s="0" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="DB13" s="0" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="DC13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DD13" s="0" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="DE13" s="0" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DF13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DG13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DH13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DI13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DJ13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK13" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DL13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DM13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DN13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DO13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DP13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DQ13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DR13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DS13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DT13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DU13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DV13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DW13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DX13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="DY13" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
       </c>
     </row>
     <row ht="12" customHeight="true" r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>M. Jalloh</t>
+          <t>R. Paunio</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -5882,21 +5826,21 @@
         </is>
       </c>
       <c r="E14" s="0" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F14" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H14" s="0" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>1354</v>
+        <v>2161</v>
       </c>
       <c r="J14" s="0" t="n">
         <v>0</v>
@@ -5911,81 +5855,81 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="0" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="O14" s="0" t="n">
         <v>75.0</v>
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="Q14" s="0" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="R14" s="0" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S14" s="0" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="T14" s="0" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="U14" s="0" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="V14" s="0" t="n">
-        <v>0.53</v>
+        <v>1.08</v>
       </c>
       <c r="W14" s="0" t="n">
-        <v>0.0</v>
+        <v>0.12</v>
       </c>
       <c r="X14" s="0" t="n">
-        <v>0.0</v>
+        <v>66.67</v>
       </c>
       <c r="Y14" s="0" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="Z14" s="0" t="n">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="AA14" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AB14" s="0" t="n">
-        <v>0.0</v>
+        <v>0.06</v>
       </c>
       <c r="AC14" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="AD14" s="0" t="n">
-        <v>0.53</v>
+        <v>0.96</v>
       </c>
       <c r="AE14" s="0" t="n">
-        <v>0.69</v>
+        <v>1.28</v>
       </c>
       <c r="AF14" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AG14" s="0" t="n">
         <v>1</v>
       </c>
       <c r="AH14" s="0" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="AI14" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="AK14" s="0" t="n">
         <v>0.0</v>
@@ -6051,7 +5995,7 @@
         <v>0.0</v>
       </c>
       <c r="BF14" s="0" t="n">
-        <v>0.07</v>
+        <v>0.12</v>
       </c>
       <c r="BG14" s="0" t="n">
         <v>100.0</v>
@@ -6060,61 +6004,61 @@
         <v>0.0</v>
       </c>
       <c r="BI14" s="0" t="n">
-        <v>0.0</v>
+        <v>0.04</v>
       </c>
       <c r="BJ14" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BK14" s="0" t="n">
-        <v>18.68</v>
+        <v>17.83</v>
       </c>
       <c r="BL14" s="0" t="n">
-        <v>0.13</v>
+        <v>0.29</v>
       </c>
       <c r="BM14" s="0" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="BN14" s="0" t="n">
-        <v>28.05</v>
+        <v>29.44</v>
       </c>
       <c r="BO14" s="0" t="n">
-        <v>81.99</v>
+        <v>83.88</v>
       </c>
       <c r="BP14" s="0" t="n">
-        <v>15.09</v>
+        <v>15.28</v>
       </c>
       <c r="BQ14" s="0" t="n">
-        <v>70.48</v>
+        <v>73.84</v>
       </c>
       <c r="BR14" s="0" t="n">
-        <v>0.07</v>
+        <v>0.0</v>
       </c>
       <c r="BS14" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="BT14" s="0" t="n">
-        <v>11.3</v>
+        <v>12.37</v>
       </c>
       <c r="BU14" s="0" t="n">
-        <v>97.06</v>
+        <v>95.29</v>
       </c>
       <c r="BV14" s="0" t="n">
-        <v>16.22</v>
+        <v>18.07</v>
       </c>
       <c r="BW14" s="0" t="n">
-        <v>96.31</v>
+        <v>97.24</v>
       </c>
       <c r="BX14" s="0" t="n">
-        <v>11.7</v>
+        <v>11.33</v>
       </c>
       <c r="BY14" s="0" t="n">
-        <v>63.07</v>
+        <v>62.87</v>
       </c>
       <c r="BZ14" s="0" t="n">
-        <v>33.58</v>
+        <v>31.18</v>
       </c>
       <c r="CA14" s="0" t="n">
-        <v>50.47</v>
+        <v>47.55</v>
       </c>
       <c r="CB14" s="0" t="n">
         <v>0.0</v>
@@ -6138,73 +6082,73 @@
         <v>0.0</v>
       </c>
       <c r="CI14" s="0" t="n">
-        <v>3.92</v>
+        <v>3.25</v>
       </c>
       <c r="CJ14" s="0" t="n">
-        <v>59.32</v>
+        <v>61.54</v>
       </c>
       <c r="CK14" s="0" t="n">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="CL14" s="0" t="n">
-        <v>25.0</v>
+        <v>50.0</v>
       </c>
       <c r="CM14" s="0" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="CN14" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CO14" s="0" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="CP14" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="CQ14" s="0" t="n">
-        <v>9.37</v>
+        <v>8.62</v>
       </c>
       <c r="CR14" s="0" t="n">
-        <v>76.6</v>
+        <v>69.08</v>
       </c>
       <c r="CS14" s="0" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="CT14" s="0" t="n">
-        <v>0.73</v>
+        <v>1.29</v>
       </c>
       <c r="CU14" s="0" t="n">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="CV14" s="0" t="n">
-        <v>3.26</v>
+        <v>4.54</v>
       </c>
       <c r="CW14" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CX14" s="0" t="n">
-        <v>77.55</v>
+        <v>71.56</v>
       </c>
       <c r="CY14" s="0" t="n">
-        <v>13.54</v>
+        <v>36.93</v>
       </c>
       <c r="CZ14" s="0" t="n">
-        <v>0.9</v>
+        <v>1.54</v>
       </c>
       <c r="DA14" s="0" t="n">
-        <v>2.54</v>
+        <v>5.93</v>
       </c>
       <c r="DB14" s="0" t="n">
-        <v>0.169</v>
+        <v>0.247</v>
       </c>
       <c r="DC14" s="0" t="n">
         <v>0.0</v>
       </c>
       <c r="DD14" s="0" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="DE14" s="0" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="DF14" s="0" t="inlineStr">
         <is>
@@ -6231,62 +6175,62 @@
         <v>0.0</v>
       </c>
       <c r="DL14" s="0" t="n">
-        <v>6279.92</v>
+        <v>3790.82</v>
       </c>
       <c r="DM14" s="0" t="n">
-        <v>197.4</v>
+        <v>16.31</v>
       </c>
       <c r="DN14" s="0" t="n">
-        <v>35.03</v>
+        <v>0.0</v>
       </c>
       <c r="DO14" s="0" t="n">
-        <v>9.29</v>
+        <v>0.0</v>
       </c>
       <c r="DP14" s="0" t="n">
-        <v>44.32</v>
+        <v>0.0</v>
       </c>
       <c r="DQ14" s="0" t="n">
-        <v>69.78</v>
+        <v>42.12</v>
       </c>
       <c r="DR14" s="0" t="n">
-        <v>31.07</v>
+        <v>19.02</v>
       </c>
       <c r="DS14" s="0" t="n">
-        <v>69.3</v>
+        <v>79.78</v>
       </c>
       <c r="DT14" s="0" t="n">
-        <v>7.91</v>
+        <v>5.77</v>
       </c>
       <c r="DU14" s="0" t="n">
-        <v>82.79</v>
+        <v>83.62</v>
       </c>
       <c r="DV14" s="0" t="n">
-        <v>6.98</v>
+        <v>9.61</v>
       </c>
       <c r="DW14" s="0" t="n">
-        <v>4.19</v>
+        <v>0.0</v>
       </c>
       <c r="DX14" s="0" t="n">
-        <v>0.93</v>
+        <v>0.0</v>
       </c>
       <c r="DY14" s="0" t="n">
-        <v>5.12</v>
+        <v>0.0</v>
       </c>
     </row>
     <row ht="12" customHeight="true" r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>O. Maukonen</t>
+          <t>K. Lund</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -6295,7 +6239,7 @@
         </is>
       </c>
       <c r="E15" s="0" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F15" s="0" t="n">
         <v>0</v>
@@ -6306,10 +6250,10 @@
         </is>
       </c>
       <c r="H15" s="0" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>1352</v>
+        <v>1624</v>
       </c>
       <c r="J15" s="0" t="n">
         <v>0</v>
@@ -6324,19 +6268,19 @@
         <v>0.0</v>
       </c>
       <c r="N15" s="0" t="n">
-        <v>0.87</v>
+        <v>0.61</v>
       </c>
       <c r="O15" s="0" t="n">
-        <v>92.31</v>
+        <v>90.91</v>
       </c>
       <c r="P15" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="Q15" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="R15" s="0" t="inlineStr">
@@ -6356,16 +6300,16 @@
         </is>
       </c>
       <c r="V15" s="0" t="n">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
       <c r="W15" s="0" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="X15" s="0" t="n">
         <v>100.0</v>
       </c>
       <c r="Y15" s="0" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="Z15" s="0" t="n">
         <v>100.0</v>
@@ -6380,19 +6324,19 @@
         <v>0.0</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.8</v>
+        <v>0.94</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.07</v>
+        <v>0.0</v>
       </c>
       <c r="AG15" s="0" t="n">
         <v>1</v>
       </c>
       <c r="AH15" s="0" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="AI15" s="0" t="n">
         <v>0</v>
@@ -6464,10 +6408,10 @@
         <v>0.0</v>
       </c>
       <c r="BF15" s="0" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="BG15" s="0" t="n">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
       <c r="BH15" s="0" t="n">
         <v>0.0</v>
@@ -6479,211 +6423,1093 @@
         <v>0.0</v>
       </c>
       <c r="BK15" s="0" t="n">
-        <v>18.57</v>
+        <v>13.63</v>
       </c>
       <c r="BL15" s="0" t="n">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="BM15" s="0" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="BN15" s="0" t="n">
-        <v>28.76</v>
+        <v>24.0</v>
       </c>
       <c r="BO15" s="0" t="n">
-        <v>83.1</v>
+        <v>78.98</v>
       </c>
       <c r="BP15" s="0" t="n">
-        <v>15.71</v>
+        <v>14.85</v>
       </c>
       <c r="BQ15" s="0" t="n">
-        <v>71.61</v>
+        <v>68.66</v>
       </c>
       <c r="BR15" s="0" t="n">
-        <v>0.07</v>
+        <v>0.0</v>
       </c>
       <c r="BS15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT15" s="0" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="BU15" s="0" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="BV15" s="0" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="BW15" s="0" t="n">
+        <v>95.15</v>
+      </c>
+      <c r="BX15" s="0" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="BY15" s="0" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="BZ15" s="0" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="CA15" s="0" t="n">
+        <v>53.09</v>
+      </c>
+      <c r="CB15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI15" s="0" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CJ15" s="0" t="n">
+        <v>36.07</v>
+      </c>
+      <c r="CK15" s="0" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CL15" s="0" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="CM15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CN15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CO15" s="0" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="CP15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CQ15" s="0" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="CR15" s="0" t="n">
+        <v>69.37</v>
+      </c>
+      <c r="CS15" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT15" s="0" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CU15" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="CV15" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="CW15" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX15" s="0" t="n">
+        <v>74.55</v>
+      </c>
+      <c r="CY15" s="0" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="CZ15" s="0" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DA15" s="0" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="DB15" s="0" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="DC15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD15" s="0" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DE15" s="0" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DF15" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DG15" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DH15" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DI15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DJ15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DL15" s="0" t="n">
+        <v>3758.44</v>
+      </c>
+      <c r="DM15" s="0" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="DN15" s="0" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="DO15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DP15" s="0" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="DQ15" s="0" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="DR15" s="0" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="DS15" s="0" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="DT15" s="0" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="DU15" s="0" t="n">
+        <v>63.61</v>
+      </c>
+      <c r="DV15" s="0" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="DW15" s="0" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DX15" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DY15" s="0" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row ht="12" customHeight="true" r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>J. Öst</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>HJK</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>HJK</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <v>519</v>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="O16" s="0" t="n">
         <v>100.0</v>
       </c>
-      <c r="BT15" s="0" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="BU15" s="0" t="n">
-        <v>97.84</v>
-      </c>
-      <c r="BV15" s="0" t="n">
-        <v>17.31</v>
-      </c>
-      <c r="BW15" s="0" t="n">
-        <v>97.31</v>
-      </c>
-      <c r="BX15" s="0" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="BY15" s="0" t="n">
-        <v>61.63</v>
-      </c>
-      <c r="BZ15" s="0" t="n">
-        <v>33.47</v>
-      </c>
-      <c r="CA15" s="0" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="CB15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CC15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CD15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CE15" s="0" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="CF15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CG15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CH15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CI15" s="0" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="CJ15" s="0" t="n">
-        <v>47.27</v>
-      </c>
-      <c r="CK15" s="0" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="CL15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CM15" s="0" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="CN15" s="0" t="n">
+      <c r="P16" s="0" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="Q16" s="0" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="R16" s="0" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="S16" s="0" t="n">
+        <v>194</v>
+      </c>
+      <c r="T16" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="U16" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="V16" s="0" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="W16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y16" s="0" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z16" s="0" t="n">
         <v>100.0</v>
       </c>
-      <c r="CO15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CP15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CQ15" s="0" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="CR15" s="0" t="n">
-        <v>73.88</v>
-      </c>
-      <c r="CS15" s="0" t="n">
+      <c r="AA16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC16" s="0" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AD16" s="0" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AE16" s="0" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="0" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AI16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AT16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF16" s="0" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BG16" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="BH16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BJ16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK16" s="0" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="BL16" s="0" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BM16" s="0" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="BN16" s="0" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BO16" s="0" t="n">
+        <v>89.51</v>
+      </c>
+      <c r="BP16" s="0" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BQ16" s="0" t="n">
+        <v>79.69</v>
+      </c>
+      <c r="BR16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT16" s="0" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="BU16" s="0" t="n">
+        <v>98.57</v>
+      </c>
+      <c r="BV16" s="0" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="BW16" s="0" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="BX16" s="0" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="BY16" s="0" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BZ16" s="0" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="CA16" s="0" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="CB16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI16" s="0" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CJ16" s="0" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="CK16" s="0" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CL16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CM16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CN16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CO16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CP16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CQ16" s="0" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="CR16" s="0" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="CS16" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT16" s="0" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CU16" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="CV16" s="0" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="CW16" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX16" s="0" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="CY16" s="0" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="CZ16" s="0" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DA16" s="0" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="DB16" s="0" t="n">
+        <v>-0.132</v>
+      </c>
+      <c r="DC16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD16" s="0" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DE16" s="0" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DF16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DG16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DH16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DI16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DJ16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DL16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DM16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DN16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DO16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DP16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DQ16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DR16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DS16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DT16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DU16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DV16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DW16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DX16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DY16" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row ht="12" customHeight="true" r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>H. Riihimäki</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>2027-12-31</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <v>380</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="0" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O17" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="P17" s="0" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="Q17" s="0" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="R17" s="0" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="S17" s="0" t="n">
+        <v>188</v>
+      </c>
+      <c r="T17" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="U17" s="0" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="V17" s="0" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Y17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD17" s="0" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AE17" s="0" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AF17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AL17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AO17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AP17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AR17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AT17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AU17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AV17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AX17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AY17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AZ17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BA17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BB17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BC17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BD17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BE17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BF17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BG17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BH17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BI17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BJ17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BK17" s="0" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="BL17" s="0" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BM17" s="0" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BN17" s="0" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="BO17" s="0" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="BP17" s="0" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="BQ17" s="0" t="n">
+        <v>59.38</v>
+      </c>
+      <c r="BR17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT17" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BU17" s="0" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="BV17" s="0" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="BW17" s="0" t="n">
+        <v>98.0</v>
+      </c>
+      <c r="BX17" s="0" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="BY17" s="0" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="BZ17" s="0" t="n">
+        <v>35.31</v>
+      </c>
+      <c r="CA17" s="0" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="CB17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CC17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CD17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CF17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CG17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CH17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CI17" s="0" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="CJ17" s="0" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="CK17" s="0" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CL17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CM17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CN17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CO17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CP17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CQ17" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="CR17" s="0" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="CS17" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="CT17" s="0" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="CU17" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="CT15" s="0" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="CU15" s="0" t="n">
-        <v>52</v>
-      </c>
-      <c r="CV15" s="0" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="CW15" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="CX15" s="0" t="n">
-        <v>71.15</v>
-      </c>
-      <c r="CY15" s="0" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="CZ15" s="0" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DA15" s="0" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="DB15" s="0" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="DC15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DD15" s="0" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DE15" s="0" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DF15" s="0" t="inlineStr">
+      <c r="CV17" s="0" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CW17" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="CX17" s="0" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="CY17" s="0" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="CZ17" s="0" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="DA17" s="0" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DB17" s="0" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="DC17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DD17" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DE17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DF17" s="0" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="DG15" s="0" t="inlineStr">
+      <c r="DG17" s="0" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="DH15" s="0" t="inlineStr">
+      <c r="DH17" s="0" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="DI15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DJ15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK15" s="0" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="DL15" s="0" t="n">
-        <v>4747.67</v>
-      </c>
-      <c r="DM15" s="0" t="n">
-        <v>67.07</v>
-      </c>
-      <c r="DN15" s="0" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="DO15" s="0" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="DP15" s="0" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="DQ15" s="0" t="n">
-        <v>52.75</v>
-      </c>
-      <c r="DR15" s="0" t="n">
-        <v>26.88</v>
-      </c>
-      <c r="DS15" s="0" t="n">
-        <v>52.78</v>
-      </c>
-      <c r="DT15" s="0" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DU15" s="0" t="n">
-        <v>52.78</v>
-      </c>
-      <c r="DV15" s="0" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="DW15" s="0" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="DX15" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="DY15" s="0" t="n">
-        <v>1.81</v>
+      <c r="DI17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DJ17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK17" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="DL17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DM17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DN17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DO17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DP17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DQ17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DR17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DS17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DT17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DU17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DV17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DW17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DX17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="DY17" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
   </sheetData>
